--- a/products/paycheck-budget-planner.xlsx
+++ b/products/paycheck-budget-planner.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Paycheck Planner" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">'Paycheck Planner'!$A$1:$M$40</definedName>
+    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">'Paycheck Planner'!$A$1:$M$41</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">Setup!$A$1:$D$26</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'Start Here'!$A$1:$H$27</definedName>
   </definedNames>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
   <si>
     <t xml:space="preserve">Paycheck Budget Planner</t>
   </si>
@@ -183,6 +183,15 @@
   </si>
   <si>
     <t xml:space="preserve">Left to assign</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bills</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Savings &amp; debt</t>
   </si>
 </sst>
 </file>
@@ -196,7 +205,7 @@
     <numFmt numFmtId="167" formatCode="mm/dd"/>
     <numFmt numFmtId="168" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -328,6 +337,20 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color rgb="FF6B7280"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FFC4B8AE"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="18"/>
       <color rgb="FF000000"/>
@@ -341,7 +364,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -357,13 +380,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFBF6F2"/>
-        <bgColor rgb="FFF4F6FA"/>
+        <bgColor rgb="FFFFFBEF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF6DE"/>
-        <bgColor rgb="FFFBF6F2"/>
+        <bgColor rgb="FFFFFBEF"/>
       </patternFill>
     </fill>
     <fill>
@@ -375,6 +398,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFBEF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFBEF"/>
         <bgColor rgb="FFFBF6F2"/>
       </patternFill>
     </fill>
@@ -437,7 +466,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="32">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -538,7 +567,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="166" fontId="17" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -552,6 +581,18 @@
     </xf>
     <xf numFmtId="168" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -611,7 +652,7 @@
       <rgbColor rgb="FFB26205"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF1B7A46"/>
-      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FFC4B8AE"/>
       <rgbColor rgb="FF878787"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF9C4A31"/>
@@ -632,11 +673,11 @@
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFF4F6FA"/>
       <rgbColor rgb="FFE5E7EB"/>
-      <rgbColor rgb="FFFBF6F2"/>
+      <rgbColor rgb="FFFFFBEF"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FFFBF6F2"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -644,9 +685,9 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFC06B45"/>
       <rgbColor rgb="FF6B7280"/>
-      <rgbColor rgb="FF93A3B8"/>
+      <rgbColor rgb="FF5C6B63"/>
       <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF2F9E6E"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FFB3352C"/>
@@ -684,7 +725,7 @@
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
-              <a:t>Income vs. assigned, check by check</a:t>
+              <a:t>Where each check goes</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -701,25 +742,25 @@
     <c:plotArea>
       <c:barChart>
         <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
+        <c:grouping val="stacked"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>"Income"</c:f>
+              <c:f>"Bills"</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Income</c:v>
+                  <c:v>Bills</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="93a3b8"/>
+              <a:srgbClr val="9c4a31"/>
             </a:solidFill>
             <a:ln w="0">
               <a:noFill/>
@@ -753,19 +794,59 @@
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>'Paycheck Planner'!$B$6:$M$6</c:f>
+              <c:f>'Paycheck Planner'!$B$43:$M$43</c:f>
               <c:multiLvlStrCache>
                 <c:ptCount val="1"/>
-                <c:lvl/>
-                <c:lvl/>
-                <c:lvl/>
-                <c:lvl/>
-                <c:lvl/>
-                <c:lvl/>
-                <c:lvl/>
-                <c:lvl/>
-                <c:lvl/>
-                <c:lvl/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>–</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>–</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>–</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>–</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>–</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>–</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>–</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>–</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>–</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>–</c:v>
+                  </c:pt>
+                </c:lvl>
                 <c:lvl>
                   <c:pt idx="0">
                     <c:v>08/21</c:v>
@@ -781,15 +862,45 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Paycheck Planner'!$B$7:$M$7</c:f>
+              <c:f>'Paycheck Planner'!$B$39:$M$39</c:f>
               <c:numCache>
-                <c:formatCode>\$#,##0</c:formatCode>
+                <c:formatCode>\$#,##0;"($"#,##0\);\-</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>1650</c:v>
+                  <c:v>1600</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1650</c:v>
+                  <c:v>235</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -800,11 +911,11 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>"Assigned"</c:f>
+              <c:f>"Spending"</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Assigned</c:v>
+                  <c:v>Spending</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -845,19 +956,59 @@
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>'Paycheck Planner'!$B$6:$M$6</c:f>
+              <c:f>'Paycheck Planner'!$B$43:$M$43</c:f>
               <c:multiLvlStrCache>
                 <c:ptCount val="1"/>
-                <c:lvl/>
-                <c:lvl/>
-                <c:lvl/>
-                <c:lvl/>
-                <c:lvl/>
-                <c:lvl/>
-                <c:lvl/>
-                <c:lvl/>
-                <c:lvl/>
-                <c:lvl/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>–</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>–</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>–</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>–</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>–</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>–</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>–</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>–</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>–</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>–</c:v>
+                  </c:pt>
+                </c:lvl>
                 <c:lvl>
                   <c:pt idx="0">
                     <c:v>08/21</c:v>
@@ -873,15 +1024,15 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Paycheck Planner'!$B$37:$M$37</c:f>
+              <c:f>'Paycheck Planner'!$B$40:$M$40</c:f>
               <c:numCache>
                 <c:formatCode>\$#,##0;"($"#,##0\);\-</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>1650</c:v>
+                  <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1650</c:v>
+                  <c:v>555</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -917,19 +1068,339 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:gapWidth val="150"/>
-        <c:overlap val="0"/>
-        <c:axId val="77341300"/>
-        <c:axId val="58558786"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"Savings &amp; debt"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Savings &amp; debt</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="2f9e6e"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'Paycheck Planner'!$B$43:$M$43</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="1"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>–</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>–</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>–</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>–</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>–</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>–</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>–</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>–</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>–</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>–</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>08/21</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>08/07</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Paycheck Planner'!$B$41:$M$41</c:f>
+              <c:numCache>
+                <c:formatCode>\$#,##0;"($"#,##0\);\-</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>860</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="55"/>
+        <c:overlap val="100"/>
+        <c:axId val="27013644"/>
+        <c:axId val="56200142"/>
       </c:barChart>
+      <c:lineChart>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"Income"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Income</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="5c6b63"/>
+            </a:solidFill>
+            <a:ln w="21960">
+              <a:solidFill>
+                <a:srgbClr val="5c6b63"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="5c6b63"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>'Paycheck Planner'!$B$43:$M$43</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="1"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>–</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>–</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>–</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>–</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>–</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>–</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>–</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>–</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>–</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>–</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>08/21</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>08/07</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Paycheck Planner'!$B$7:$M$7</c:f>
+              <c:numCache>
+                <c:formatCode>\$#,##0</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>1650</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1650</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:hiLowLines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:hiLowLines>
+        <c:marker val="1"/>
+        <c:axId val="27013644"/>
+        <c:axId val="56200142"/>
+      </c:lineChart>
       <c:catAx>
-        <c:axId val="77341300"/>
+        <c:axId val="27013644"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="mm/dd" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -955,7 +1426,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="58558786"/>
+        <c:crossAx val="56200142"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -963,7 +1434,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="58558786"/>
+        <c:axId val="56200142"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1005,7 +1476,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="77341300"/>
+        <c:crossAx val="27013644"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1017,7 +1488,7 @@
       </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="r"/>
+      <c:legendPos val="b"/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1060,14 +1531,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>506880</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>11520</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>306360</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>162000</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1075,8 +1546,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="8458200"/>
-        <a:ext cx="5759640" cy="2735640"/>
+        <a:off x="0" y="9210600"/>
+        <a:ext cx="6299640" cy="3095640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2154,7 +2625,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:N58"/>
+  <dimension ref="A1:N62"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="16.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
@@ -2948,51 +3419,165 @@
       <c r="N38" s="2"/>
     </row>
     <row r="39" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="2"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
-      <c r="J39" s="2"/>
-      <c r="K39" s="2"/>
-      <c r="L39" s="2"/>
-      <c r="M39" s="2"/>
+      <c r="A39" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="B39" s="30" t="n">
+        <f aca="false">SUM(B10:B21)</f>
+        <v>1600</v>
+      </c>
+      <c r="C39" s="30" t="n">
+        <f aca="false">SUM(C10:C21)</f>
+        <v>235</v>
+      </c>
+      <c r="D39" s="30" t="n">
+        <f aca="false">SUM(D10:D21)</f>
+        <v>0</v>
+      </c>
+      <c r="E39" s="30" t="n">
+        <f aca="false">SUM(E10:E21)</f>
+        <v>0</v>
+      </c>
+      <c r="F39" s="30" t="n">
+        <f aca="false">SUM(F10:F21)</f>
+        <v>0</v>
+      </c>
+      <c r="G39" s="30" t="n">
+        <f aca="false">SUM(G10:G21)</f>
+        <v>0</v>
+      </c>
+      <c r="H39" s="30" t="n">
+        <f aca="false">SUM(H10:H21)</f>
+        <v>0</v>
+      </c>
+      <c r="I39" s="30" t="n">
+        <f aca="false">SUM(I10:I21)</f>
+        <v>0</v>
+      </c>
+      <c r="J39" s="30" t="n">
+        <f aca="false">SUM(J10:J21)</f>
+        <v>0</v>
+      </c>
+      <c r="K39" s="30" t="n">
+        <f aca="false">SUM(K10:K21)</f>
+        <v>0</v>
+      </c>
+      <c r="L39" s="30" t="n">
+        <f aca="false">SUM(L10:L21)</f>
+        <v>0</v>
+      </c>
+      <c r="M39" s="30" t="n">
+        <f aca="false">SUM(M10:M21)</f>
+        <v>0</v>
+      </c>
       <c r="N39" s="2"/>
     </row>
     <row r="40" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2"/>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="2"/>
-      <c r="K40" s="2"/>
-      <c r="L40" s="2"/>
-      <c r="M40" s="2"/>
+      <c r="A40" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="B40" s="30" t="n">
+        <f aca="false">SUM(B23:B30)</f>
+        <v>40</v>
+      </c>
+      <c r="C40" s="30" t="n">
+        <f aca="false">SUM(C23:C30)</f>
+        <v>555</v>
+      </c>
+      <c r="D40" s="30" t="n">
+        <f aca="false">SUM(D23:D30)</f>
+        <v>0</v>
+      </c>
+      <c r="E40" s="30" t="n">
+        <f aca="false">SUM(E23:E30)</f>
+        <v>0</v>
+      </c>
+      <c r="F40" s="30" t="n">
+        <f aca="false">SUM(F23:F30)</f>
+        <v>0</v>
+      </c>
+      <c r="G40" s="30" t="n">
+        <f aca="false">SUM(G23:G30)</f>
+        <v>0</v>
+      </c>
+      <c r="H40" s="30" t="n">
+        <f aca="false">SUM(H23:H30)</f>
+        <v>0</v>
+      </c>
+      <c r="I40" s="30" t="n">
+        <f aca="false">SUM(I23:I30)</f>
+        <v>0</v>
+      </c>
+      <c r="J40" s="30" t="n">
+        <f aca="false">SUM(J23:J30)</f>
+        <v>0</v>
+      </c>
+      <c r="K40" s="30" t="n">
+        <f aca="false">SUM(K23:K30)</f>
+        <v>0</v>
+      </c>
+      <c r="L40" s="30" t="n">
+        <f aca="false">SUM(L23:L30)</f>
+        <v>0</v>
+      </c>
+      <c r="M40" s="30" t="n">
+        <f aca="false">SUM(M23:M30)</f>
+        <v>0</v>
+      </c>
       <c r="N40" s="2"/>
     </row>
     <row r="41" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="2"/>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
-      <c r="J41" s="2"/>
-      <c r="K41" s="2"/>
-      <c r="L41" s="2"/>
-      <c r="M41" s="2"/>
+      <c r="A41" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="B41" s="30" t="n">
+        <f aca="false">SUM(B32:B35)</f>
+        <v>10</v>
+      </c>
+      <c r="C41" s="30" t="n">
+        <f aca="false">SUM(C32:C35)</f>
+        <v>860</v>
+      </c>
+      <c r="D41" s="30" t="n">
+        <f aca="false">SUM(D32:D35)</f>
+        <v>0</v>
+      </c>
+      <c r="E41" s="30" t="n">
+        <f aca="false">SUM(E32:E35)</f>
+        <v>0</v>
+      </c>
+      <c r="F41" s="30" t="n">
+        <f aca="false">SUM(F32:F35)</f>
+        <v>0</v>
+      </c>
+      <c r="G41" s="30" t="n">
+        <f aca="false">SUM(G32:G35)</f>
+        <v>0</v>
+      </c>
+      <c r="H41" s="30" t="n">
+        <f aca="false">SUM(H32:H35)</f>
+        <v>0</v>
+      </c>
+      <c r="I41" s="30" t="n">
+        <f aca="false">SUM(I32:I35)</f>
+        <v>0</v>
+      </c>
+      <c r="J41" s="30" t="n">
+        <f aca="false">SUM(J32:J35)</f>
+        <v>0</v>
+      </c>
+      <c r="K41" s="30" t="n">
+        <f aca="false">SUM(K32:K35)</f>
+        <v>0</v>
+      </c>
+      <c r="L41" s="30" t="n">
+        <f aca="false">SUM(L32:L35)</f>
+        <v>0</v>
+      </c>
+      <c r="M41" s="30" t="n">
+        <f aca="false">SUM(M32:M35)</f>
+        <v>0</v>
+      </c>
       <c r="N41" s="2"/>
     </row>
     <row r="42" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3011,20 +3596,56 @@
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
     </row>
-    <row r="43" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="2"/>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
-      <c r="J43" s="2"/>
-      <c r="K43" s="2"/>
-      <c r="L43" s="2"/>
-      <c r="M43" s="2"/>
+      <c r="B43" s="31" t="str">
+        <f aca="false">IF(B$6="","–",TEXT(B$6,"mm/dd"))</f>
+        <v>08/07</v>
+      </c>
+      <c r="C43" s="31" t="str">
+        <f aca="false">IF(C$6="","–",TEXT(C$6,"mm/dd"))</f>
+        <v>08/21</v>
+      </c>
+      <c r="D43" s="31" t="str">
+        <f aca="false">IF(D$6="","–",TEXT(D$6,"mm/dd"))</f>
+        <v>–</v>
+      </c>
+      <c r="E43" s="31" t="str">
+        <f aca="false">IF(E$6="","–",TEXT(E$6,"mm/dd"))</f>
+        <v>–</v>
+      </c>
+      <c r="F43" s="31" t="str">
+        <f aca="false">IF(F$6="","–",TEXT(F$6,"mm/dd"))</f>
+        <v>–</v>
+      </c>
+      <c r="G43" s="31" t="str">
+        <f aca="false">IF(G$6="","–",TEXT(G$6,"mm/dd"))</f>
+        <v>–</v>
+      </c>
+      <c r="H43" s="31" t="str">
+        <f aca="false">IF(H$6="","–",TEXT(H$6,"mm/dd"))</f>
+        <v>–</v>
+      </c>
+      <c r="I43" s="31" t="str">
+        <f aca="false">IF(I$6="","–",TEXT(I$6,"mm/dd"))</f>
+        <v>–</v>
+      </c>
+      <c r="J43" s="31" t="str">
+        <f aca="false">IF(J$6="","–",TEXT(J$6,"mm/dd"))</f>
+        <v>–</v>
+      </c>
+      <c r="K43" s="31" t="str">
+        <f aca="false">IF(K$6="","–",TEXT(K$6,"mm/dd"))</f>
+        <v>–</v>
+      </c>
+      <c r="L43" s="31" t="str">
+        <f aca="false">IF(L$6="","–",TEXT(L$6,"mm/dd"))</f>
+        <v>–</v>
+      </c>
+      <c r="M43" s="31" t="str">
+        <f aca="false">IF(M$6="","–",TEXT(M$6,"mm/dd"))</f>
+        <v>–</v>
+      </c>
       <c r="N43" s="2"/>
     </row>
     <row r="44" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3266,6 +3887,70 @@
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
       <c r="N58" s="2"/>
+    </row>
+    <row r="59" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="2"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
+      <c r="I59" s="2"/>
+      <c r="J59" s="2"/>
+      <c r="K59" s="2"/>
+      <c r="L59" s="2"/>
+      <c r="M59" s="2"/>
+      <c r="N59" s="2"/>
+    </row>
+    <row r="60" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="2"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+      <c r="I60" s="2"/>
+      <c r="J60" s="2"/>
+      <c r="K60" s="2"/>
+      <c r="L60" s="2"/>
+      <c r="M60" s="2"/>
+      <c r="N60" s="2"/>
+    </row>
+    <row r="61" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="2"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
+      <c r="I61" s="2"/>
+      <c r="J61" s="2"/>
+      <c r="K61" s="2"/>
+      <c r="L61" s="2"/>
+      <c r="M61" s="2"/>
+      <c r="N61" s="2"/>
+    </row>
+    <row r="62" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="2"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
+      <c r="I62" s="2"/>
+      <c r="J62" s="2"/>
+      <c r="K62" s="2"/>
+      <c r="L62" s="2"/>
+      <c r="M62" s="2"/>
+      <c r="N62" s="2"/>
     </row>
   </sheetData>
   <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false"/>

--- a/products/paycheck-budget-planner.xlsx
+++ b/products/paycheck-budget-planner.xlsx
@@ -299,8 +299,8 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="9"/>
+      <color rgb="FF9C4A31"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
@@ -408,7 +408,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -417,17 +417,20 @@
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
-      <left style="thin">
-        <color rgb="FFD8DEE9"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD8DEE9"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD8DEE9"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
-        <color rgb="FFD8DEE9"/>
+        <color rgb="FFE7EBEE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF9C4A31"/>
       </bottom>
       <diagonal/>
     </border>
@@ -527,7 +530,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -543,7 +546,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="15" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -575,7 +578,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="14" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -657,11 +660,11 @@
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF9C4A31"/>
       <rgbColor rgb="FFFFF6DE"/>
-      <rgbColor rgb="FFE4E9E6"/>
+      <rgbColor rgb="FFE7EBEE"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFD8DEE9"/>
+      <rgbColor rgb="FFF4F6FA"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -671,7 +674,7 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFF4F6FA"/>
+      <rgbColor rgb="FFE4E9E6"/>
       <rgbColor rgb="FFE5E7EB"/>
       <rgbColor rgb="FFFFFBEF"/>
       <rgbColor rgb="FF99CCFF"/>
@@ -1232,8 +1235,8 @@
         </c:ser>
         <c:gapWidth val="55"/>
         <c:overlap val="100"/>
-        <c:axId val="27013644"/>
-        <c:axId val="56200142"/>
+        <c:axId val="18656702"/>
+        <c:axId val="18130421"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="stacked"/>
@@ -1390,11 +1393,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="27013644"/>
-        <c:axId val="56200142"/>
+        <c:axId val="18656702"/>
+        <c:axId val="18130421"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="27013644"/>
+        <c:axId val="18656702"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1426,7 +1429,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="56200142"/>
+        <c:crossAx val="18130421"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1434,7 +1437,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="56200142"/>
+        <c:axId val="18130421"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1476,7 +1479,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="27013644"/>
+        <c:crossAx val="18656702"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2398,7 +2401,7 @@
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
     </row>
-    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
         <v>26</v>
       </c>
